--- a/NMB_Map/src/algorithm/data/nodes/nodes.xlsx
+++ b/NMB_Map/src/algorithm/data/nodes/nodes.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\code\python\Pathfinding algorithms\data\nodes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\code\软件工程\NMBNavigation-Backend\NMB_Map\src\algorithm\data\nodes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E616E1-AECF-4DA5-BBC2-02ADEA49BF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{903E5834-B97F-4099-AC49-432BD93C4C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="600" yWindow="1140" windowWidth="17280" windowHeight="8964" firstSheet="21" activeTab="34" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1766" uniqueCount="951">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1768" uniqueCount="955">
   <si>
     <t>4,6</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3871,6 +3871,22 @@
   </si>
   <si>
     <t>G521,G522</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>38,6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,39</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>38,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,39</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -20638,7 +20654,7 @@
         <v>932</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>573</v>
+        <v>954</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -20656,7 +20672,7 @@
         <v>935</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>0</v>
+        <v>951</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -21193,6 +21209,9 @@
       <c r="D39" s="1" t="s">
         <v>934</v>
       </c>
+      <c r="E39" s="1" t="s">
+        <v>952</v>
+      </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
@@ -21207,10 +21226,14 @@
       <c r="D40" s="1" t="s">
         <v>933</v>
       </c>
+      <c r="E40" s="1" t="s">
+        <v>953</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/NMB_Map/src/algorithm/data/nodes/nodes.xlsx
+++ b/NMB_Map/src/algorithm/data/nodes/nodes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\code\软件工程\NMBNavigation-Backend\NMB_Map\src\algorithm\data\nodes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{903E5834-B97F-4099-AC49-432BD93C4C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3CC9930-8B98-4775-AA72-E6E5C0D86298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="1140" windowWidth="17280" windowHeight="8964" firstSheet="21" activeTab="34" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="A1" sheetId="1" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1768" uniqueCount="955">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="962">
   <si>
     <t>4,6</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1514,10 +1514,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>7,19,13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>4,10,14</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1558,10 +1554,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>8,20,21</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>19,22</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3887,6 +3879,42 @@
   </si>
   <si>
     <t>2,39</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11,20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11,12,16,19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16,42</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>42,19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17,18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7,51,13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>51,20,21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>19,8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4872,7 +4900,7 @@
         <v>176</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>91</v>
@@ -4903,7 +4931,7 @@
         <v>421</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>52</v>
@@ -4920,7 +4948,7 @@
         <v>691</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>0</v>
@@ -4937,7 +4965,7 @@
         <v>945</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>143</v>
@@ -4968,7 +4996,7 @@
         <v>1158</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>228</v>
@@ -4985,10 +5013,10 @@
         <v>1344</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5002,7 +5030,7 @@
         <v>2148</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5044,7 +5072,7 @@
         <v>2542</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>95</v>
@@ -5061,7 +5089,7 @@
         <v>2760</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>148</v>
@@ -5092,7 +5120,7 @@
         <v>3020</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>230</v>
@@ -5109,7 +5137,7 @@
         <v>3273</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>15</v>
@@ -5126,7 +5154,7 @@
         <v>3494</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>231</v>
@@ -5157,7 +5185,7 @@
         <v>3494</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="E21" s="1">
         <v>19</v>
@@ -5174,7 +5202,7 @@
         <v>3308</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>233</v>
@@ -5191,7 +5219,7 @@
         <v>2725</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>234</v>
@@ -5208,7 +5236,7 @@
         <v>2541</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>235</v>
@@ -5225,7 +5253,7 @@
         <v>2288</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>236</v>
@@ -5256,7 +5284,7 @@
         <v>2148</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>238</v>
@@ -5385,7 +5413,7 @@
         <v>1368</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>70</v>
@@ -5402,7 +5430,7 @@
         <v>1187</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>246</v>
@@ -5419,7 +5447,7 @@
         <v>1007</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>247</v>
@@ -5436,7 +5464,7 @@
         <v>850</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>248</v>
@@ -5481,7 +5509,7 @@
         <v>442</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>250</v>
@@ -5512,7 +5540,7 @@
         <v>285</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>252</v>
@@ -5557,10 +5585,10 @@
         <v>1643</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -5574,10 +5602,10 @@
         <v>1885</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
   </sheetData>
@@ -6074,7 +6102,7 @@
         <v>1156</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>278</v>
@@ -6506,7 +6534,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00A97849-E435-4CEC-9136-C5E4631D363D}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -6538,7 +6566,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>277</v>
+        <v>953</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -6552,7 +6580,7 @@
         <v>191</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>91</v>
@@ -6584,7 +6612,7 @@
         <v>352</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>52</v>
@@ -6601,7 +6629,7 @@
         <v>520</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>0</v>
@@ -6648,7 +6676,7 @@
         <v>1166</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>228</v>
@@ -6665,7 +6693,7 @@
         <v>1166</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="E10" s="1">
         <v>8</v>
@@ -6682,7 +6710,7 @@
         <v>1166</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="E11" s="1">
         <v>15</v>
@@ -6790,7 +6818,7 @@
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>283</v>
+        <v>955</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -6804,10 +6832,38 @@
         <v>1166</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>284</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1">
+        <v>425</v>
+      </c>
+      <c r="C20" s="1">
+        <v>438</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1">
+        <v>425</v>
+      </c>
+      <c r="C21" s="1">
+        <v>191</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>954</v>
       </c>
     </row>
   </sheetData>
@@ -6866,7 +6922,7 @@
         <v>191</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>91</v>
@@ -6897,7 +6953,7 @@
         <v>352</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>52</v>
@@ -6914,10 +6970,10 @@
         <v>520</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -6959,7 +7015,7 @@
         <v>1166</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>228</v>
@@ -6976,7 +7032,7 @@
         <v>1166</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="E10" s="1">
         <v>8</v>
@@ -6993,7 +7049,7 @@
         <v>1166</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="E11" s="1">
         <v>15</v>
@@ -7108,7 +7164,7 @@
         <v>1166</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>284</v>
@@ -7125,10 +7181,10 @@
         <v>814</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -7142,10 +7198,10 @@
         <v>1093</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
     </row>
   </sheetData>
@@ -7156,7 +7212,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B21573F0-4097-4877-B238-7F64CEECC0E1}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7464,7 +7520,7 @@
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>15</v>
+        <v>956</v>
       </c>
       <c r="F18" s="1"/>
     </row>
@@ -7480,7 +7536,7 @@
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>231</v>
+        <v>957</v>
       </c>
       <c r="F19" s="1"/>
     </row>
@@ -7875,6 +7931,20 @@
         <v>39</v>
       </c>
       <c r="F42" s="1"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1">
+        <v>104</v>
+      </c>
+      <c r="C43" s="1">
+        <v>610</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>958</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7884,7 +7954,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E393132A-FDD4-485D-87F7-B6B3947EC051}">
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -8032,7 +8102,7 @@
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>361</v>
+        <v>959</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -8050,7 +8120,7 @@
         <v>334</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -8066,7 +8136,7 @@
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -8082,7 +8152,7 @@
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -8098,7 +8168,7 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -8113,10 +8183,10 @@
         <v>424</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -8132,7 +8202,7 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -8148,7 +8218,7 @@
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -8164,7 +8234,7 @@
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -8180,7 +8250,7 @@
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -8195,10 +8265,10 @@
         <v>534</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -8214,7 +8284,7 @@
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>372</v>
+        <v>960</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -8248,7 +8318,7 @@
         <v>353</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -8320,7 +8390,7 @@
         <v>349</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -8370,7 +8440,7 @@
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -8404,7 +8474,7 @@
         <v>345</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -8422,7 +8492,7 @@
         <v>344</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -8440,7 +8510,7 @@
         <v>343</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -8456,7 +8526,7 @@
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -8474,7 +8544,7 @@
         <v>342</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -8492,7 +8562,7 @@
         <v>341</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -8510,7 +8580,7 @@
         <v>339</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -8526,7 +8596,7 @@
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -8576,7 +8646,7 @@
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -8608,7 +8678,7 @@
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -8624,7 +8694,7 @@
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -8658,7 +8728,7 @@
         <v>340</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -8676,7 +8746,7 @@
         <v>346</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -8694,7 +8764,7 @@
         <v>347</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -8710,7 +8780,7 @@
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -8726,7 +8796,7 @@
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -8743,12 +8813,28 @@
         <v>335</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1">
+        <v>1181</v>
+      </c>
+      <c r="C52" s="1">
+        <v>260</v>
+      </c>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1" t="s">
+        <v>961</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8803,10 +8889,10 @@
         <v>357</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -8821,7 +8907,7 @@
         <v>357</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>13</v>
@@ -8839,7 +8925,7 @@
         <v>357</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>52</v>
@@ -8857,7 +8943,7 @@
         <v>357</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>0</v>
@@ -8875,7 +8961,7 @@
         <v>357</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>1</v>
@@ -8893,7 +8979,7 @@
         <v>357</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>2</v>
@@ -8911,7 +8997,7 @@
         <v>357</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -8941,7 +9027,7 @@
         <v>357</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -8956,7 +9042,7 @@
         <v>588</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -8971,7 +9057,7 @@
         <v>588</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -8986,7 +9072,7 @@
         <v>588</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -9016,7 +9102,7 @@
         <v>359</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -9046,10 +9132,10 @@
         <v>359</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -9064,7 +9150,7 @@
         <v>359</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>231</v>
@@ -9082,7 +9168,7 @@
         <v>359</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>100</v>
@@ -9100,7 +9186,7 @@
         <v>359</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>101</v>
@@ -9118,10 +9204,10 @@
         <v>359</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -9136,7 +9222,7 @@
         <v>359</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>154</v>
@@ -9169,7 +9255,7 @@
         <v>747</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -9184,7 +9270,7 @@
         <v>830</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -9214,7 +9300,7 @@
         <v>830</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -9259,7 +9345,7 @@
         <v>895</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>108</v>
@@ -9277,10 +9363,10 @@
         <v>895</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -9295,7 +9381,7 @@
         <v>895</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>30</v>
@@ -9313,10 +9399,10 @@
         <v>895</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -9331,10 +9417,10 @@
         <v>895</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -9349,7 +9435,7 @@
         <v>895</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>70</v>
@@ -9367,10 +9453,10 @@
         <v>895</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -9385,10 +9471,10 @@
         <v>895</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -9403,10 +9489,10 @@
         <v>895</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -9421,10 +9507,10 @@
         <v>895</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -9439,7 +9525,7 @@
         <v>895</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -9454,7 +9540,7 @@
         <v>895</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -9469,7 +9555,7 @@
         <v>895</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>198</v>
@@ -9487,10 +9573,10 @@
         <v>895</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -9505,10 +9591,10 @@
         <v>895</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -9523,10 +9609,10 @@
         <v>895</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -9541,7 +9627,7 @@
         <v>895</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -9571,10 +9657,10 @@
         <v>895</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -9589,10 +9675,10 @@
         <v>895</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -9607,10 +9693,10 @@
         <v>895</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -9640,7 +9726,7 @@
         <v>895</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -9655,7 +9741,7 @@
         <v>895</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -9729,10 +9815,10 @@
         <v>357</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -9747,7 +9833,7 @@
         <v>357</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>13</v>
@@ -9765,7 +9851,7 @@
         <v>357</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>52</v>
@@ -9783,7 +9869,7 @@
         <v>357</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>0</v>
@@ -9801,7 +9887,7 @@
         <v>357</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>1</v>
@@ -9819,7 +9905,7 @@
         <v>357</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>2</v>
@@ -9838,7 +9924,7 @@
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -9870,7 +9956,7 @@
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -9886,7 +9972,7 @@
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -9902,7 +9988,7 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -9918,7 +10004,7 @@
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -9950,7 +10036,7 @@
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -9981,10 +10067,10 @@
         <v>359</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -9999,7 +10085,7 @@
         <v>359</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>231</v>
@@ -10017,7 +10103,7 @@
         <v>359</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>100</v>
@@ -10035,7 +10121,7 @@
         <v>359</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>101</v>
@@ -10053,10 +10139,10 @@
         <v>359</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -10071,7 +10157,7 @@
         <v>359</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>154</v>
@@ -10106,7 +10192,7 @@
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -10122,7 +10208,7 @@
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -10154,7 +10240,7 @@
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -10201,7 +10287,7 @@
         <v>895</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>108</v>
@@ -10219,10 +10305,10 @@
         <v>895</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -10237,7 +10323,7 @@
         <v>895</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>30</v>
@@ -10255,10 +10341,10 @@
         <v>895</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -10273,10 +10359,10 @@
         <v>895</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -10291,7 +10377,7 @@
         <v>895</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>70</v>
@@ -10309,10 +10395,10 @@
         <v>895</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -10327,10 +10413,10 @@
         <v>895</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -10345,10 +10431,10 @@
         <v>895</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -10363,10 +10449,10 @@
         <v>895</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -10382,7 +10468,7 @@
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -10398,7 +10484,7 @@
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -10413,7 +10499,7 @@
         <v>895</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>198</v>
@@ -10431,10 +10517,10 @@
         <v>895</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -10449,10 +10535,10 @@
         <v>895</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -10467,10 +10553,10 @@
         <v>895</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -10486,7 +10572,7 @@
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -10517,10 +10603,10 @@
         <v>895</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -10535,10 +10621,10 @@
         <v>895</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -10553,10 +10639,10 @@
         <v>895</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -10588,7 +10674,7 @@
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -10604,7 +10690,7 @@
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -11310,10 +11396,10 @@
         <v>357</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -11328,7 +11414,7 @@
         <v>357</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>13</v>
@@ -11346,7 +11432,7 @@
         <v>357</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>52</v>
@@ -11364,7 +11450,7 @@
         <v>357</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>0</v>
@@ -11382,7 +11468,7 @@
         <v>357</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>1</v>
@@ -11400,7 +11486,7 @@
         <v>357</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>2</v>
@@ -11419,7 +11505,7 @@
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -11451,7 +11537,7 @@
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -11467,7 +11553,7 @@
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -11483,7 +11569,7 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -11499,7 +11585,7 @@
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -11531,7 +11617,7 @@
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -11562,10 +11648,10 @@
         <v>359</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -11580,7 +11666,7 @@
         <v>359</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>231</v>
@@ -11598,7 +11684,7 @@
         <v>359</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>100</v>
@@ -11616,7 +11702,7 @@
         <v>359</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>101</v>
@@ -11634,10 +11720,10 @@
         <v>359</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -11652,7 +11738,7 @@
         <v>359</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>154</v>
@@ -11687,7 +11773,7 @@
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -11703,7 +11789,7 @@
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -11735,7 +11821,7 @@
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -11782,7 +11868,7 @@
         <v>895</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>108</v>
@@ -11800,10 +11886,10 @@
         <v>895</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -11818,7 +11904,7 @@
         <v>895</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>30</v>
@@ -11836,10 +11922,10 @@
         <v>895</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -11854,10 +11940,10 @@
         <v>895</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -11872,7 +11958,7 @@
         <v>895</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>70</v>
@@ -11890,10 +11976,10 @@
         <v>895</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -11908,10 +11994,10 @@
         <v>895</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -11926,10 +12012,10 @@
         <v>895</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -11944,10 +12030,10 @@
         <v>895</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -11963,7 +12049,7 @@
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -11979,7 +12065,7 @@
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -11994,7 +12080,7 @@
         <v>895</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>198</v>
@@ -12012,10 +12098,10 @@
         <v>895</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -12030,10 +12116,10 @@
         <v>895</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -12048,10 +12134,10 @@
         <v>895</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -12067,7 +12153,7 @@
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -12098,10 +12184,10 @@
         <v>895</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -12116,10 +12202,10 @@
         <v>895</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -12134,10 +12220,10 @@
         <v>895</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -12169,7 +12255,7 @@
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -12185,7 +12271,7 @@
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -12246,7 +12332,7 @@
         <v>167</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E2" s="1">
         <v>2</v>
@@ -12264,7 +12350,7 @@
         <v>326</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>91</v>
@@ -12282,7 +12368,7 @@
         <v>536</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -12297,7 +12383,7 @@
         <v>536</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -12327,7 +12413,7 @@
         <v>536</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -12372,10 +12458,10 @@
         <v>848</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -12390,7 +12476,7 @@
         <v>848</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -12405,7 +12491,7 @@
         <v>848</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>5</v>
@@ -12423,7 +12509,7 @@
         <v>848</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>6</v>
@@ -12441,7 +12527,7 @@
         <v>848</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>7</v>
@@ -12517,7 +12603,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -12532,7 +12618,7 @@
         <v>180</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>91</v>
@@ -12567,7 +12653,7 @@
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -12582,7 +12668,7 @@
         <v>1000</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>0</v>
@@ -12601,7 +12687,7 @@
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -12616,7 +12702,7 @@
         <v>1000</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>2</v>
@@ -12634,7 +12720,7 @@
         <v>1000</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>14</v>
@@ -12652,7 +12738,7 @@
         <v>1000</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>3</v>
@@ -12671,7 +12757,7 @@
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -12686,7 +12772,7 @@
         <v>477</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>5</v>
@@ -12704,10 +12790,10 @@
         <v>308</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -12739,7 +12825,7 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -12755,7 +12841,7 @@
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -12846,7 +12932,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -12861,7 +12947,7 @@
         <v>180</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>91</v>
@@ -12896,7 +12982,7 @@
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -12911,7 +12997,7 @@
         <v>1000</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>0</v>
@@ -12930,7 +13016,7 @@
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -12945,7 +13031,7 @@
         <v>1000</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>2</v>
@@ -12963,7 +13049,7 @@
         <v>1000</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>14</v>
@@ -12981,7 +13067,7 @@
         <v>1000</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>3</v>
@@ -13000,7 +13086,7 @@
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -13015,7 +13101,7 @@
         <v>477</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>5</v>
@@ -13033,10 +13119,10 @@
         <v>308</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -13068,7 +13154,7 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -13084,7 +13170,7 @@
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -13175,7 +13261,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -13190,7 +13276,7 @@
         <v>180</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>91</v>
@@ -13225,7 +13311,7 @@
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -13240,7 +13326,7 @@
         <v>1000</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>0</v>
@@ -13259,7 +13345,7 @@
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -13274,7 +13360,7 @@
         <v>1000</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>2</v>
@@ -13292,7 +13378,7 @@
         <v>1000</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>14</v>
@@ -13310,7 +13396,7 @@
         <v>1000</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>3</v>
@@ -13329,7 +13415,7 @@
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -13344,7 +13430,7 @@
         <v>477</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>5</v>
@@ -13362,10 +13448,10 @@
         <v>308</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -13397,7 +13483,7 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -13413,7 +13499,7 @@
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -13506,7 +13592,7 @@
         <v>180</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -13521,7 +13607,7 @@
         <v>180</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>91</v>
@@ -13554,7 +13640,7 @@
         <v>680</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -13569,7 +13655,7 @@
         <v>1000</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>0</v>
@@ -13587,7 +13673,7 @@
         <v>1000</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -13602,7 +13688,7 @@
         <v>1000</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>2</v>
@@ -13620,7 +13706,7 @@
         <v>1000</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>14</v>
@@ -13638,7 +13724,7 @@
         <v>1000</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>3</v>
@@ -13656,7 +13742,7 @@
         <v>1000</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -13671,10 +13757,10 @@
         <v>477</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -13689,10 +13775,10 @@
         <v>308</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -13722,7 +13808,7 @@
         <v>887</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -13737,7 +13823,7 @@
         <v>680</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -13796,10 +13882,10 @@
         <v>934</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -13813,10 +13899,10 @@
         <v>713</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
   </sheetData>
@@ -13858,7 +13944,7 @@
         <v>3217</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E2" s="1">
         <v>2</v>
@@ -13876,7 +13962,7 @@
         <v>3035</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>91</v>
@@ -13895,7 +13981,7 @@
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -13926,10 +14012,10 @@
         <v>2301</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -13976,7 +14062,7 @@
         <v>2054</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>228</v>
@@ -13995,7 +14081,7 @@
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -14010,7 +14096,7 @@
         <v>1292</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>4</v>
@@ -14028,7 +14114,7 @@
         <v>1084</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>5</v>
@@ -14047,7 +14133,7 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -14078,7 +14164,7 @@
         <v>366</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>96</v>
@@ -14097,7 +14183,7 @@
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -14112,10 +14198,10 @@
         <v>151</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -14131,7 +14217,7 @@
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -14146,10 +14232,10 @@
         <v>240</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -14181,7 +14267,7 @@
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -14197,7 +14283,7 @@
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -14244,10 +14330,10 @@
         <v>844</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -14262,10 +14348,10 @@
         <v>1026</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -14296,7 +14382,7 @@
         <v>1272</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E28" s="1">
         <v>26</v>
@@ -14315,7 +14401,7 @@
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -14331,7 +14417,7 @@
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -14379,7 +14465,7 @@
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -14394,7 +14480,7 @@
         <v>2269</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E34" s="1">
         <v>32</v>
@@ -14412,10 +14498,10 @@
         <v>2525</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -14430,7 +14516,7 @@
         <v>2712</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>70</v>
@@ -14526,10 +14612,10 @@
         <v>3555</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -14544,7 +14630,7 @@
         <v>3412</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -14559,7 +14645,7 @@
         <v>3213</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>13</v>
@@ -14577,7 +14663,7 @@
         <v>2658</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -14607,7 +14693,7 @@
         <v>2392</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>293</v>
@@ -14655,7 +14741,7 @@
         <v>2069</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -14670,7 +14756,7 @@
         <v>1317</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>4</v>
@@ -14688,7 +14774,7 @@
         <v>1074</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>5</v>
@@ -14706,7 +14792,7 @@
         <v>902</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -14736,7 +14822,7 @@
         <v>360</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>96</v>
@@ -14754,7 +14840,7 @@
         <v>227</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -14769,10 +14855,10 @@
         <v>142</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -14787,10 +14873,10 @@
         <v>227</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -14805,10 +14891,10 @@
         <v>227</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -14838,7 +14924,7 @@
         <v>227</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -14853,7 +14939,7 @@
         <v>533</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -14898,10 +14984,10 @@
         <v>828</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -14916,10 +15002,10 @@
         <v>1011</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -14949,7 +15035,7 @@
         <v>1242</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E28" s="1">
         <v>26</v>
@@ -14967,7 +15053,7 @@
         <v>1713</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -14982,7 +15068,7 @@
         <v>1713</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -15027,7 +15113,7 @@
         <v>1920</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -15042,7 +15128,7 @@
         <v>2067</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -15057,7 +15143,7 @@
         <v>2422</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -15072,7 +15158,7 @@
         <v>2517</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>70</v>
@@ -15090,7 +15176,7 @@
         <v>2709</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>246</v>
@@ -15108,7 +15194,7 @@
         <v>3036</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -15153,7 +15239,7 @@
         <v>3412</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -15168,7 +15254,7 @@
         <v>3555</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -15183,10 +15269,10 @@
         <v>3412</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -15201,10 +15287,10 @@
         <v>3412</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -15219,10 +15305,10 @@
         <v>2422</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -15237,7 +15323,7 @@
         <v>2067</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -15252,10 +15338,10 @@
         <v>2067</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -15270,10 +15356,10 @@
         <v>2067</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
   </sheetData>
@@ -15318,10 +15404,10 @@
         <v>236</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -15336,7 +15422,7 @@
         <v>236</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -15351,7 +15437,7 @@
         <v>236</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="E4" s="1">
         <v>2</v>
@@ -15369,10 +15455,10 @@
         <v>360</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -15387,7 +15473,7 @@
         <v>640</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -15417,10 +15503,10 @@
         <v>940</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -15435,7 +15521,7 @@
         <v>1136</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>14</v>
@@ -15453,7 +15539,7 @@
         <v>1320</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>3</v>
@@ -15501,7 +15587,7 @@
         <v>1760</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -15516,7 +15602,7 @@
         <v>1760</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -15561,7 +15647,7 @@
         <v>1960</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -15591,7 +15677,7 @@
         <v>2100</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -15606,7 +15692,7 @@
         <v>2268</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>100</v>
@@ -15624,7 +15710,7 @@
         <v>2471</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>101</v>
@@ -15642,10 +15728,10 @@
         <v>2629</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -15660,7 +15746,7 @@
         <v>2825</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>154</v>
@@ -15708,7 +15794,7 @@
         <v>3250</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>156</v>
@@ -15741,7 +15827,7 @@
         <v>3445</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E28" s="1">
         <v>26</v>
@@ -15759,7 +15845,7 @@
         <v>3445</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>190</v>
@@ -15777,7 +15863,7 @@
         <v>3247</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>28</v>
@@ -15795,7 +15881,7 @@
         <v>2987</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>108</v>
@@ -15813,10 +15899,10 @@
         <v>2728</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -15846,10 +15932,10 @@
         <v>2487</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -15894,7 +15980,7 @@
         <v>2100</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -15909,10 +15995,10 @@
         <v>2100</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -15927,10 +16013,10 @@
         <v>1320</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -15945,10 +16031,10 @@
         <v>1132</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -15963,10 +16049,10 @@
         <v>920</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -15996,10 +16082,10 @@
         <v>663</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -16014,7 +16100,7 @@
         <v>411</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>252</v>
@@ -16062,10 +16148,10 @@
         <v>236</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -16080,7 +16166,7 @@
         <v>236</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -16095,7 +16181,7 @@
         <v>236</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="E4" s="1">
         <v>2</v>
@@ -16113,10 +16199,10 @@
         <v>360</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -16131,7 +16217,7 @@
         <v>640</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -16161,10 +16247,10 @@
         <v>940</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -16179,7 +16265,7 @@
         <v>1136</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>14</v>
@@ -16197,7 +16283,7 @@
         <v>1320</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>3</v>
@@ -16245,7 +16331,7 @@
         <v>1760</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -16260,7 +16346,7 @@
         <v>1760</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -16305,7 +16391,7 @@
         <v>1960</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -16335,7 +16421,7 @@
         <v>2100</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -16350,7 +16436,7 @@
         <v>2268</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>100</v>
@@ -16368,7 +16454,7 @@
         <v>2471</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>101</v>
@@ -16386,10 +16472,10 @@
         <v>2629</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -16404,7 +16490,7 @@
         <v>2825</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>154</v>
@@ -16452,7 +16538,7 @@
         <v>3250</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>156</v>
@@ -16485,7 +16571,7 @@
         <v>3445</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="E28" s="1">
         <v>26</v>
@@ -16503,7 +16589,7 @@
         <v>3445</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>190</v>
@@ -16521,7 +16607,7 @@
         <v>3247</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>28</v>
@@ -16539,7 +16625,7 @@
         <v>2987</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>108</v>
@@ -16557,10 +16643,10 @@
         <v>2728</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -16590,10 +16676,10 @@
         <v>2487</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -16638,7 +16724,7 @@
         <v>2100</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -16653,10 +16739,10 @@
         <v>2100</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -16671,10 +16757,10 @@
         <v>1320</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -16689,10 +16775,10 @@
         <v>1132</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -16707,10 +16793,10 @@
         <v>920</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -16740,10 +16826,10 @@
         <v>663</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -16758,7 +16844,7 @@
         <v>411</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>252</v>
@@ -17386,10 +17472,10 @@
         <v>236</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -17404,7 +17490,7 @@
         <v>236</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -17419,7 +17505,7 @@
         <v>236</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="E4" s="1">
         <v>2</v>
@@ -17437,10 +17523,10 @@
         <v>360</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -17455,7 +17541,7 @@
         <v>640</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -17485,10 +17571,10 @@
         <v>940</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -17503,7 +17589,7 @@
         <v>1136</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>14</v>
@@ -17521,7 +17607,7 @@
         <v>1320</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>3</v>
@@ -17569,7 +17655,7 @@
         <v>1760</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -17584,7 +17670,7 @@
         <v>1760</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -17629,7 +17715,7 @@
         <v>1960</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -17659,7 +17745,7 @@
         <v>2100</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -17674,7 +17760,7 @@
         <v>2268</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>100</v>
@@ -17692,7 +17778,7 @@
         <v>2471</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>101</v>
@@ -17710,10 +17796,10 @@
         <v>2629</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -17728,7 +17814,7 @@
         <v>2825</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>154</v>
@@ -17776,7 +17862,7 @@
         <v>3250</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>156</v>
@@ -17809,7 +17895,7 @@
         <v>3445</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="E28" s="1">
         <v>26</v>
@@ -17827,7 +17913,7 @@
         <v>3445</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>190</v>
@@ -17845,7 +17931,7 @@
         <v>3247</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>28</v>
@@ -17863,7 +17949,7 @@
         <v>2987</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>108</v>
@@ -17881,10 +17967,10 @@
         <v>2728</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -17914,10 +18000,10 @@
         <v>2487</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -17962,7 +18048,7 @@
         <v>2100</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -17977,10 +18063,10 @@
         <v>2100</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -17995,10 +18081,10 @@
         <v>1320</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -18013,10 +18099,10 @@
         <v>1132</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -18031,10 +18117,10 @@
         <v>920</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -18064,10 +18150,10 @@
         <v>663</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -18082,7 +18168,7 @@
         <v>411</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>252</v>
@@ -18099,10 +18185,10 @@
         <v>1860</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -18116,10 +18202,10 @@
         <v>1622</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
   </sheetData>
@@ -18164,10 +18250,10 @@
         <v>348</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -18182,7 +18268,7 @@
         <v>348</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>91</v>
@@ -18200,7 +18286,7 @@
         <v>348</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>13</v>
@@ -18218,7 +18304,7 @@
         <v>348</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>52</v>
@@ -18236,7 +18322,7 @@
         <v>348</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -18251,7 +18337,7 @@
         <v>348</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>1</v>
@@ -18269,7 +18355,7 @@
         <v>348</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>2</v>
@@ -18287,7 +18373,7 @@
         <v>348</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>14</v>
@@ -18305,7 +18391,7 @@
         <v>348</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>3</v>
@@ -18383,10 +18469,10 @@
         <v>478</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -18416,7 +18502,7 @@
         <v>870</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -18431,7 +18517,7 @@
         <v>870</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -18476,10 +18562,10 @@
         <v>870</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -18494,10 +18580,10 @@
         <v>870</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -18527,7 +18613,7 @@
         <v>870</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -18557,10 +18643,10 @@
         <v>1144</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -18590,7 +18676,7 @@
         <v>907</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -18620,10 +18706,10 @@
         <v>851</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -18638,7 +18724,7 @@
         <v>560</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -18653,7 +18739,7 @@
         <v>560</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -18668,7 +18754,7 @@
         <v>560</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -18683,10 +18769,10 @@
         <v>471</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -18701,7 +18787,7 @@
         <v>736</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -18762,10 +18848,10 @@
         <v>1130</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -18780,7 +18866,7 @@
         <v>907</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -18810,10 +18896,10 @@
         <v>847</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -18828,7 +18914,7 @@
         <v>341</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>0</v>
@@ -18846,7 +18932,7 @@
         <v>341</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>1</v>
@@ -18864,7 +18950,7 @@
         <v>341</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>2</v>
@@ -18882,7 +18968,7 @@
         <v>341</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>14</v>
@@ -18900,7 +18986,7 @@
         <v>341</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -18915,7 +19001,7 @@
         <v>341</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>4</v>
@@ -18933,7 +19019,7 @@
         <v>341</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>5</v>
@@ -18951,7 +19037,7 @@
         <v>341</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>6</v>
@@ -18969,7 +19055,7 @@
         <v>341</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>7</v>
@@ -18987,7 +19073,7 @@
         <v>341</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>269</v>
@@ -19005,7 +19091,7 @@
         <v>341</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>97</v>
@@ -19023,7 +19109,7 @@
         <v>341</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>282</v>
@@ -19041,7 +19127,7 @@
         <v>341</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -19101,7 +19187,7 @@
         <v>861</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -19146,10 +19232,10 @@
         <v>861</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -19164,10 +19250,10 @@
         <v>861</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -19182,7 +19268,7 @@
         <v>861</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>16</v>
@@ -19200,7 +19286,7 @@
         <v>861</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>17</v>
@@ -19218,7 +19304,7 @@
         <v>861</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -19233,7 +19319,7 @@
         <v>1130</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -19248,7 +19334,7 @@
         <v>730</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -19278,7 +19364,7 @@
         <v>547</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -19307,7 +19393,7 @@
         <v>1130</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -19321,10 +19407,10 @@
         <v>445</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
   </sheetData>
@@ -19366,10 +19452,10 @@
         <v>1130</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -19385,7 +19471,7 @@
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -19416,10 +19502,10 @@
         <v>847</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -19434,7 +19520,7 @@
         <v>341</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>0</v>
@@ -19452,7 +19538,7 @@
         <v>341</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>1</v>
@@ -19470,7 +19556,7 @@
         <v>341</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>2</v>
@@ -19488,7 +19574,7 @@
         <v>341</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>14</v>
@@ -19507,7 +19593,7 @@
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -19522,7 +19608,7 @@
         <v>341</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>4</v>
@@ -19556,7 +19642,7 @@
         <v>341</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>6</v>
@@ -19574,7 +19660,7 @@
         <v>341</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>7</v>
@@ -19592,7 +19678,7 @@
         <v>341</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>269</v>
@@ -19610,7 +19696,7 @@
         <v>341</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>97</v>
@@ -19628,7 +19714,7 @@
         <v>341</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>282</v>
@@ -19647,7 +19733,7 @@
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -19711,7 +19797,7 @@
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -19758,10 +19844,10 @@
         <v>861</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -19776,10 +19862,10 @@
         <v>861</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -19794,7 +19880,7 @@
         <v>861</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>16</v>
@@ -19829,7 +19915,7 @@
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -19845,7 +19931,7 @@
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -19861,7 +19947,7 @@
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -19893,7 +19979,7 @@
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -19924,7 +20010,7 @@
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -19938,10 +20024,10 @@
         <v>445</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
   </sheetData>
@@ -19983,10 +20069,10 @@
         <v>1130</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -20002,7 +20088,7 @@
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -20033,10 +20119,10 @@
         <v>847</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -20051,7 +20137,7 @@
         <v>341</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>0</v>
@@ -20069,7 +20155,7 @@
         <v>341</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>1</v>
@@ -20087,7 +20173,7 @@
         <v>341</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>2</v>
@@ -20105,7 +20191,7 @@
         <v>341</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>14</v>
@@ -20124,7 +20210,7 @@
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -20139,7 +20225,7 @@
         <v>341</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>4</v>
@@ -20173,7 +20259,7 @@
         <v>341</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>6</v>
@@ -20191,7 +20277,7 @@
         <v>341</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>7</v>
@@ -20209,7 +20295,7 @@
         <v>341</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>269</v>
@@ -20227,7 +20313,7 @@
         <v>341</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>97</v>
@@ -20245,7 +20331,7 @@
         <v>341</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>282</v>
@@ -20264,7 +20350,7 @@
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -20328,7 +20414,7 @@
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -20375,10 +20461,10 @@
         <v>861</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -20393,10 +20479,10 @@
         <v>861</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -20411,7 +20497,7 @@
         <v>861</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>16</v>
@@ -20446,7 +20532,7 @@
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -20462,7 +20548,7 @@
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -20478,7 +20564,7 @@
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -20510,7 +20596,7 @@
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -20541,7 +20627,7 @@
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -20555,10 +20641,10 @@
         <v>445</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
   </sheetData>
@@ -20603,10 +20689,10 @@
         <v>1130</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -20621,7 +20707,7 @@
         <v>907</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -20651,10 +20737,10 @@
         <v>847</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -20669,10 +20755,10 @@
         <v>341</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -20687,7 +20773,7 @@
         <v>341</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>1</v>
@@ -20705,7 +20791,7 @@
         <v>341</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>2</v>
@@ -20723,7 +20809,7 @@
         <v>341</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>14</v>
@@ -20741,7 +20827,7 @@
         <v>341</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -20756,7 +20842,7 @@
         <v>341</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>4</v>
@@ -20789,7 +20875,7 @@
         <v>341</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>6</v>
@@ -20807,7 +20893,7 @@
         <v>341</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>7</v>
@@ -20825,7 +20911,7 @@
         <v>341</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>269</v>
@@ -20843,7 +20929,7 @@
         <v>341</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>97</v>
@@ -20861,7 +20947,7 @@
         <v>341</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>282</v>
@@ -20879,7 +20965,7 @@
         <v>341</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -20939,7 +21025,7 @@
         <v>861</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -20984,10 +21070,10 @@
         <v>861</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -21002,10 +21088,10 @@
         <v>861</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -21020,10 +21106,10 @@
         <v>861</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -21053,7 +21139,7 @@
         <v>861</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -21068,7 +21154,7 @@
         <v>1130</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -21083,7 +21169,7 @@
         <v>730</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -21113,7 +21199,7 @@
         <v>547</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -21142,7 +21228,7 @@
         <v>1130</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -21156,10 +21242,10 @@
         <v>445</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -21173,10 +21259,10 @@
         <v>861</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -21190,10 +21276,10 @@
         <v>861</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -21207,10 +21293,10 @@
         <v>406</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -21224,10 +21310,10 @@
         <v>636</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
   </sheetData>
@@ -21315,7 +21401,7 @@
         <v>413</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>52</v>
@@ -21332,7 +21418,7 @@
         <v>413</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>0</v>
@@ -21349,7 +21435,7 @@
         <v>413</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>1</v>
@@ -21366,7 +21452,7 @@
         <v>413</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>2</v>
@@ -21383,7 +21469,7 @@
         <v>413</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>14</v>
@@ -21400,7 +21486,7 @@
         <v>413</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>3</v>
@@ -21417,7 +21503,7 @@
         <v>413</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>93</v>
@@ -21434,7 +21520,7 @@
         <v>413</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>94</v>
@@ -21451,7 +21537,7 @@
         <v>413</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>95</v>
@@ -21468,7 +21554,7 @@
         <v>413</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>96</v>
@@ -21485,7 +21571,7 @@
         <v>413</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>97</v>
@@ -21502,7 +21588,7 @@
         <v>1156</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>98</v>
@@ -21549,7 +21635,7 @@
         <v>1417</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>100</v>
@@ -21656,7 +21742,7 @@
         <v>590</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>105</v>
@@ -21688,7 +21774,7 @@
         <v>1085</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>107</v>
@@ -21705,7 +21791,7 @@
         <v>1085</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>28</v>
@@ -21722,7 +21808,7 @@
         <v>1085</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>108</v>
@@ -21873,7 +21959,7 @@
         <v>413</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>52</v>
@@ -21890,7 +21976,7 @@
         <v>413</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>0</v>
@@ -21907,7 +21993,7 @@
         <v>413</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>1</v>
@@ -21924,7 +22010,7 @@
         <v>413</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>2</v>
@@ -21941,7 +22027,7 @@
         <v>413</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>14</v>
@@ -21958,7 +22044,7 @@
         <v>413</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>3</v>
@@ -21975,7 +22061,7 @@
         <v>413</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>93</v>
@@ -21992,7 +22078,7 @@
         <v>413</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>94</v>
@@ -22009,7 +22095,7 @@
         <v>413</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>95</v>
@@ -22026,7 +22112,7 @@
         <v>413</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>96</v>
@@ -22043,10 +22129,10 @@
         <v>413</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -22060,10 +22146,10 @@
         <v>1156</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -22107,7 +22193,7 @@
         <v>1417</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>100</v>
@@ -22214,7 +22300,7 @@
         <v>590</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>105</v>
@@ -22246,10 +22332,10 @@
         <v>1085</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -22263,10 +22349,10 @@
         <v>1085</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -22280,7 +22366,7 @@
         <v>1085</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>108</v>
@@ -22357,10 +22443,10 @@
         <v>500</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -22374,10 +22460,10 @@
         <v>768</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -22391,10 +22477,10 @@
         <v>1085</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -22408,10 +22494,10 @@
         <v>1085</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
   </sheetData>
@@ -24557,7 +24643,7 @@
         <v>176</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>91</v>
@@ -24588,7 +24674,7 @@
         <v>421</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>52</v>
@@ -24605,7 +24691,7 @@
         <v>691</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>0</v>
@@ -24622,7 +24708,7 @@
         <v>945</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>143</v>
@@ -24653,7 +24739,7 @@
         <v>1158</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>228</v>
@@ -24670,7 +24756,7 @@
         <v>1344</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>3</v>
@@ -24729,7 +24815,7 @@
         <v>2542</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>95</v>
@@ -24746,7 +24832,7 @@
         <v>2760</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>148</v>
@@ -24777,7 +24863,7 @@
         <v>3020</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>230</v>
@@ -24794,7 +24880,7 @@
         <v>3273</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>15</v>
@@ -24811,7 +24897,7 @@
         <v>3494</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>231</v>
@@ -24842,7 +24928,7 @@
         <v>3494</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="E21" s="1">
         <v>19</v>
@@ -24859,7 +24945,7 @@
         <v>3308</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>233</v>
@@ -24876,7 +24962,7 @@
         <v>2725</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>234</v>
@@ -24893,7 +24979,7 @@
         <v>2541</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>235</v>
@@ -24910,7 +24996,7 @@
         <v>2288</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>236</v>
@@ -24941,7 +25027,7 @@
         <v>2148</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>238</v>
@@ -25070,7 +25156,7 @@
         <v>1368</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>70</v>
@@ -25087,7 +25173,7 @@
         <v>1187</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>246</v>
@@ -25104,7 +25190,7 @@
         <v>1007</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>247</v>
@@ -25121,7 +25207,7 @@
         <v>850</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>248</v>
@@ -25166,7 +25252,7 @@
         <v>442</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>250</v>
@@ -25197,7 +25283,7 @@
         <v>285</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>252</v>
